--- a/data/trans_camb/P3A_R1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,86</t>
+          <t>2,33; 17,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 18,39</t>
+          <t>3,69; 18,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 12,17</t>
+          <t>-2,61; 12,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -1,08</t>
+          <t>-11,65; -0,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 4,91</t>
+          <t>-7,19; 4,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 18,3</t>
+          <t>5,48; 17,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 6,53</t>
+          <t>-2,65; 7,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 9,96</t>
+          <t>-0,14; 10,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 12,77</t>
+          <t>3,52; 12,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 97,26</t>
+          <t>10,06; 105,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 113,74</t>
+          <t>16,27; 118,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 75,6</t>
+          <t>-12,19; 78,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,07; -6,8</t>
+          <t>-63,33; -1,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 43,61</t>
+          <t>-40,45; 43,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 166,57</t>
+          <t>27,35; 149,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 43,98</t>
+          <t>-13,29; 48,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 65,39</t>
+          <t>-1,02; 69,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 85,94</t>
+          <t>17,27; 85,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 4,5</t>
+          <t>-6,41; 4,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 9,9</t>
+          <t>-1,85; 9,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 21,71</t>
+          <t>8,12; 21,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 3,23</t>
+          <t>-5,39; 3,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,27</t>
+          <t>-2,43; 5,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,76; 20,94</t>
+          <t>11,64; 21,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,79</t>
+          <t>-5,12; 2,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 6,5</t>
+          <t>-1,26; 6,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 19,78</t>
+          <t>11,58; 19,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 20,86</t>
+          <t>-22,76; 22,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 44,55</t>
+          <t>-7,31; 42,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,32; 92,54</t>
+          <t>27,76; 94,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 26,9</t>
+          <t>-34,25; 32,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 53,1</t>
+          <t>-15,14; 51,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,21; 181,78</t>
+          <t>71,2; 178,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 15,49</t>
+          <t>-23,15; 15,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 36,17</t>
+          <t>-5,88; 35,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,38; 110,41</t>
+          <t>53,01; 113,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 13,63</t>
+          <t>0,18; 13,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 29,38</t>
+          <t>15,03; 28,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 20,96</t>
+          <t>7,48; 21,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 7,05</t>
+          <t>-1,57; 7,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 19,61</t>
+          <t>9,1; 19,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,97; 25,61</t>
+          <t>15,47; 25,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 8,58</t>
+          <t>0,45; 8,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 22,73</t>
+          <t>14,06; 22,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,97; 21,69</t>
+          <t>13,41; 21,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 88,04</t>
+          <t>0,77; 87,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64,05; 189,64</t>
+          <t>65,1; 185,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,03; 135,19</t>
+          <t>29,9; 133,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 128,4</t>
+          <t>-18,72; 133,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84,88; 331,29</t>
+          <t>84,13; 338,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>156,22; 457,57</t>
+          <t>142,38; 467,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,98; 79,57</t>
+          <t>2,49; 77,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,27; 208,28</t>
+          <t>92,45; 198,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82,96; 198,31</t>
+          <t>83,24; 190,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 15,96</t>
+          <t>2,62; 15,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 17,47</t>
+          <t>5,04; 18,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 20,31</t>
+          <t>4,15; 19,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,72; -0,87</t>
+          <t>-11,06; -0,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -0,52</t>
+          <t>-10,41; -0,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 1,52</t>
+          <t>-11,12; 1,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 5,96</t>
+          <t>-2,69; 5,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 7,15</t>
+          <t>-1,24; 6,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 7,71</t>
+          <t>-4,56; 7,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 89,5</t>
+          <t>10,78; 90,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,73; 100,04</t>
+          <t>19,94; 106,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,8; 115,67</t>
+          <t>18,07; 110,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,85; -5,61</t>
+          <t>-51,9; -4,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,18; -2,13</t>
+          <t>-50,54; 0,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,03; 9,48</t>
+          <t>-52,37; 9,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 33,61</t>
+          <t>-12,44; 31,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 41,68</t>
+          <t>-5,8; 38,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 42,04</t>
+          <t>-22,12; 39,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 6,22</t>
+          <t>-10,18; 6,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,03; 24,48</t>
+          <t>6,89; 23,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 10,55</t>
+          <t>-4,99; 10,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 10,52</t>
+          <t>-1,79; 10,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,67</t>
+          <t>1,5; 14,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 13,94</t>
+          <t>-2,14; 14,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 6,45</t>
+          <t>-3,76; 6,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,62; 17,59</t>
+          <t>6,31; 16,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 9,34</t>
+          <t>-2,97; 10,0</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 38,97</t>
+          <t>-40,27; 37,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>29,3; 163,87</t>
+          <t>26,06; 138,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 63,74</t>
+          <t>-19,91; 64,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 139,15</t>
+          <t>-15,6; 143,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,29; 201,65</t>
+          <t>8,39; 198,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 171,1</t>
+          <t>-15,54; 178,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 49,65</t>
+          <t>-20,65; 45,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>30,41; 138,0</t>
+          <t>34,17; 126,08</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 69,33</t>
+          <t>-15,2; 77,5</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,46; 19,94</t>
+          <t>4,53; 19,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,82; 15,04</t>
+          <t>0,05; 14,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15,25; 29,27</t>
+          <t>15,75; 29,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 11,36</t>
+          <t>-0,56; 11,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 4,23</t>
+          <t>-6,71; 4,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,38; 29,9</t>
+          <t>18,21; 30,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,4; 14,08</t>
+          <t>3,93; 13,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 7,2</t>
+          <t>-1,37; 7,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18,7; 28,51</t>
+          <t>19,21; 28,38</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23,71; 135,38</t>
+          <t>22,96; 133,57</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,71; 103,67</t>
+          <t>-0,16; 98,88</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>70,95; 212,14</t>
+          <t>74,14; 215,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 109,17</t>
+          <t>-4,98; 111,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 41,16</t>
+          <t>-43,86; 43,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>102,71; 301,01</t>
+          <t>108,87; 305,77</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,31; 106,28</t>
+          <t>22,53; 105,71</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 55,27</t>
+          <t>-7,64; 57,45</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>102,69; 219,12</t>
+          <t>106,51; 225,42</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 8,44</t>
+          <t>-1,37; 9,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 10,32</t>
+          <t>-0,19; 10,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 9,54</t>
+          <t>-1,31; 9,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,38; 11,39</t>
+          <t>3,39; 11,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,71; 16,66</t>
+          <t>8,71; 16,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 14,46</t>
+          <t>-2,44; 14,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,79</t>
+          <t>2,4; 8,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,66; 12,1</t>
+          <t>5,75; 12,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 9,94</t>
+          <t>-3,14; 10,15</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 39,84</t>
+          <t>-4,66; 44,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,26; 48,54</t>
+          <t>-1,03; 50,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 46,08</t>
+          <t>-4,37; 43,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25,32; 124,81</t>
+          <t>25,92; 124,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>67,13; 185,35</t>
+          <t>68,3; 195,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 145,42</t>
+          <t>-19,77; 146,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,79; 56,64</t>
+          <t>12,96; 55,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>29,98; 77,58</t>
+          <t>31,19; 81,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 61,41</t>
+          <t>-16,49; 62,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,15; 16,11</t>
+          <t>6,86; 16,03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12,7; 21,74</t>
+          <t>12,71; 21,88</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -0,23</t>
+          <t>-16,31; -0,21</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,87; 11,0</t>
+          <t>4,27; 11,19</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>8,39; 15,58</t>
+          <t>9,05; 15,58</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,04; -2,34</t>
+          <t>-6,99; -2,3</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,78; 12,33</t>
+          <t>6,44; 12,34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>11,89; 17,63</t>
+          <t>11,97; 17,79</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -1,92</t>
+          <t>-8,84; -1,73</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>34,41; 99,06</t>
+          <t>32,56; 95,95</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>60,73; 133,31</t>
+          <t>61,59; 134,39</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,06; -0,92</t>
+          <t>-71,72; -1,08</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31,64; 132,55</t>
+          <t>38,59; 134,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>74,46; 191,26</t>
+          <t>79,39; 185,62</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-62,55; -26,7</t>
+          <t>-61,95; -27,88</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,23; 96,87</t>
+          <t>41,69; 97,88</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>78,02; 140,59</t>
+          <t>77,21; 141,3</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-57,36; -14,96</t>
+          <t>-58,47; -13,21</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,58</t>
+          <t>4,46; 8,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,72</t>
+          <t>9,25; 13,67</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 9,15</t>
+          <t>-0,4; 9,17</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,68</t>
+          <t>1,13; 4,61</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,33</t>
+          <t>4,63; 8,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,93</t>
+          <t>4,0; 9,91</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,1</t>
+          <t>3,38; 6,05</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,4</t>
+          <t>7,56; 10,44</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,84</t>
+          <t>3,67; 8,8</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>20,02; 43,51</t>
+          <t>20,36; 43,8</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>41,62; 69,44</t>
+          <t>42,96; 68,43</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 45,14</t>
+          <t>-0,3; 44,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10,48; 41,85</t>
+          <t>8,47; 41,36</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>37,28; 73,99</t>
+          <t>35,58; 73,03</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>33,86; 88,13</t>
+          <t>33,88; 87,42</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>19,14; 38,24</t>
+          <t>20,03; 38,89</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>44,28; 66,23</t>
+          <t>43,86; 66,39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>22,94; 55,89</t>
+          <t>23,41; 55,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,81</t>
+          <t>9,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>7,14</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 17,06</t>
+          <t>2,48; 17,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 18,7</t>
+          <t>3,12; 18,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 12,36</t>
+          <t>-2,73; 11,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,65; -0,3</t>
+          <t>-12,11; -0,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 4,75</t>
+          <t>-7,76; 5,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 17,77</t>
+          <t>4,25; 15,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 7,06</t>
+          <t>-2,86; 6,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 10,15</t>
+          <t>-0,32; 9,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,97</t>
+          <t>2,71; 11,48</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,06; 105,71</t>
+          <t>9,22; 102,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,27; 118,76</t>
+          <t>12,53; 109,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 78,22</t>
+          <t>-11,25; 69,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-63,33; -1,02</t>
+          <t>-65,5; -2,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 43,1</t>
+          <t>-42,74; 48,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,35; 149,46</t>
+          <t>21,41; 128,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 48,8</t>
+          <t>-14,03; 45,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 69,53</t>
+          <t>-1,53; 65,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,27; 85,42</t>
+          <t>12,88; 76,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,0</t>
+          <t>16,44</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,41</t>
+          <t>17,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,78</t>
+          <t>16,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 4,92</t>
+          <t>-6,19; 4,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 9,8</t>
+          <t>-1,66; 9,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 21,32</t>
+          <t>9,46; 22,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,9</t>
+          <t>-5,28; 3,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 5,92</t>
+          <t>-2,86; 6,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,64; 21,23</t>
+          <t>12,38; 21,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 2,62</t>
+          <t>-4,49; 2,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 6,38</t>
+          <t>-0,64; 6,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 19,9</t>
+          <t>12,73; 20,56</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>116,26%</t>
+          <t>120,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 22,44</t>
+          <t>-23,11; 20,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 42,52</t>
+          <t>-5,9; 41,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,76; 94,75</t>
+          <t>32,74; 102,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 32,7</t>
+          <t>-34,31; 30,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 51,08</t>
+          <t>-17,51; 50,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,2; 178,65</t>
+          <t>76,74; 188,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 15,3</t>
+          <t>-21,07; 13,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 35,5</t>
+          <t>-2,97; 35,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,01; 113,11</t>
+          <t>58,46; 117,1</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>13,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,68</t>
+          <t>21,44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,53</t>
+          <t>17,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 13,16</t>
+          <t>0,9; 13,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,03; 28,76</t>
+          <t>14,12; 28,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 21,09</t>
+          <t>7,34; 21,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 7,6</t>
+          <t>-1,57; 7,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 19,54</t>
+          <t>9,2; 19,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,47; 25,33</t>
+          <t>16,17; 26,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 8,71</t>
+          <t>0,76; 8,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,06; 22,53</t>
+          <t>13,78; 22,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 21,7</t>
+          <t>13,31; 21,51</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>266,2%</t>
+          <t>276,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>134,16%</t>
+          <t>134,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 87,49</t>
+          <t>3,72; 86,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,1; 185,79</t>
+          <t>63,0; 190,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,9; 133,49</t>
+          <t>33,4; 137,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 133,21</t>
+          <t>-17,17; 134,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84,13; 338,81</t>
+          <t>92,21; 351,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>142,38; 467,22</t>
+          <t>154,19; 475,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 77,68</t>
+          <t>4,69; 80,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>92,45; 198,8</t>
+          <t>89,92; 204,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83,24; 190,65</t>
+          <t>87,9; 192,75</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,85</t>
+          <t>11,11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>5,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 15,94</t>
+          <t>2,43; 15,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 18,25</t>
+          <t>4,77; 18,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 19,57</t>
+          <t>3,43; 18,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -0,69</t>
+          <t>-11,47; -0,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -0,06</t>
+          <t>-11,42; -0,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 1,78</t>
+          <t>-5,82; 4,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 5,55</t>
+          <t>-2,95; 5,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,92</t>
+          <t>-1,46; 6,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 7,18</t>
+          <t>0,82; 9,47</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-21,48%</t>
+          <t>-0,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,78; 90,44</t>
+          <t>8,65; 90,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,94; 106,64</t>
+          <t>19,34; 107,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,07; 110,49</t>
+          <t>14,89; 106,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,9; -4,36</t>
+          <t>-53,4; -2,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,54; 0,57</t>
+          <t>-51,45; -0,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,37; 9,91</t>
+          <t>-26,94; 30,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 31,69</t>
+          <t>-13,89; 30,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 38,72</t>
+          <t>-7,35; 36,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 39,53</t>
+          <t>3,64; 53,6</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>11,73</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>7,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 6,47</t>
+          <t>-9,53; 6,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,89; 23,62</t>
+          <t>6,62; 23,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 10,38</t>
+          <t>-5,06; 9,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 10,89</t>
+          <t>-2,03; 10,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,76</t>
+          <t>0,86; 14,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 14,89</t>
+          <t>6,0; 17,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 6,1</t>
+          <t>-4,01; 6,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,31; 16,92</t>
+          <t>6,4; 17,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 10,0</t>
+          <t>2,28; 11,46</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>109,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 37,24</t>
+          <t>-38,7; 40,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>26,06; 138,99</t>
+          <t>24,57; 143,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 64,77</t>
+          <t>-21,09; 59,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 143,94</t>
+          <t>-16,54; 134,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,39; 198,19</t>
+          <t>4,82; 187,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 178,37</t>
+          <t>38,87; 248,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 45,16</t>
+          <t>-22,1; 46,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>34,17; 126,08</t>
+          <t>32,16; 134,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 77,5</t>
+          <t>11,98; 89,12</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22,66</t>
+          <t>23,08</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,23</t>
+          <t>23,8</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23,52</t>
+          <t>23,5</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,53; 19,34</t>
+          <t>5,74; 20,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,05; 14,78</t>
+          <t>1,15; 15,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15,75; 29,59</t>
+          <t>16,21; 29,79</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 11,98</t>
+          <t>-0,3; 12,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 4,49</t>
+          <t>-6,83; 3,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,21; 30,57</t>
+          <t>16,98; 29,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,93; 13,9</t>
+          <t>3,92; 13,94</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,79</t>
+          <t>-1,53; 7,38</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19,21; 28,38</t>
+          <t>18,95; 27,94</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>128,84%</t>
+          <t>131,22%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>187,39%</t>
+          <t>184,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>154,41%</t>
+          <t>154,28%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22,96; 133,57</t>
+          <t>26,88; 143,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 98,88</t>
+          <t>4,52; 105,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74,14; 215,64</t>
+          <t>76,06; 210,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 111,48</t>
+          <t>-2,28; 117,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 43,36</t>
+          <t>-46,23; 39,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>108,87; 305,77</t>
+          <t>101,13; 295,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,53; 105,71</t>
+          <t>21,27; 106,11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 57,45</t>
+          <t>-9,26; 57,68</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106,51; 225,42</t>
+          <t>101,28; 214,64</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,48</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,3</t>
+          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 9,27</t>
+          <t>-1,25; 9,15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 10,76</t>
+          <t>-0,05; 10,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 9,02</t>
+          <t>0,17; 11,11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,04</t>
+          <t>3,6; 11,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,71; 16,52</t>
+          <t>8,6; 16,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 14,36</t>
+          <t>9,15; 16,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,53</t>
+          <t>2,36; 8,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,51</t>
+          <t>5,59; 12,1</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 10,15</t>
+          <t>5,88; 12,19</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>118,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 44,32</t>
+          <t>-5,2; 43,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 50,44</t>
+          <t>-0,13; 51,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 43,9</t>
+          <t>0,63; 53,03</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25,92; 124,14</t>
+          <t>29,33; 127,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>68,3; 195,57</t>
+          <t>70,56; 192,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 146,35</t>
+          <t>69,1; 188,24</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,96; 55,53</t>
+          <t>13,22; 57,71</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>31,19; 81,84</t>
+          <t>30,59; 78,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 62,04</t>
+          <t>31,1; 78,52</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-6,13</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-4,53</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-4,72</t>
+          <t>-3,05</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,86; 16,03</t>
+          <t>7,04; 15,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12,71; 21,88</t>
+          <t>13,21; 22,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -0,21</t>
+          <t>-5,56; 2,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,27; 11,19</t>
+          <t>4,23; 10,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,05; 15,58</t>
+          <t>8,67; 15,78</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -2,3</t>
+          <t>-7,06; -2,22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,44; 12,34</t>
+          <t>6,57; 12,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>11,97; 17,79</t>
+          <t>11,86; 17,59</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,84; -1,73</t>
+          <t>-5,47; -0,72</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-32,98%</t>
+          <t>-8,43%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-46,98%</t>
+          <t>-47,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-33,8%</t>
+          <t>-21,85%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>32,56; 95,95</t>
+          <t>32,28; 94,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>61,59; 134,39</t>
+          <t>64,86; 138,75</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-71,72; -1,08</t>
+          <t>-27,05; 16,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38,59; 134,78</t>
+          <t>37,51; 133,24</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>79,39; 185,62</t>
+          <t>76,59; 195,32</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-61,95; -27,88</t>
+          <t>-63,0; -26,86</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,69; 97,88</t>
+          <t>44,17; 96,36</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>77,21; 141,3</t>
+          <t>77,14; 137,59</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-58,47; -13,21</t>
+          <t>-35,84; -6,11</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>8,12</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,82</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>8,69</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,73</t>
+          <t>4,29; 8,86</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9,25; 13,67</t>
+          <t>9,26; 13,72</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,17</t>
+          <t>5,79; 10,22</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,61</t>
+          <t>1,18; 4,74</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,27</t>
+          <t>4,87; 8,4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,91</t>
+          <t>7,72; 10,9</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,05</t>
+          <t>3,37; 6,16</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,44</t>
+          <t>7,44; 10,39</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,8</t>
+          <t>7,32; 10,08</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>20,36; 43,8</t>
+          <t>19,46; 44,61</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>42,96; 68,43</t>
+          <t>42,03; 68,57</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 44,96</t>
+          <t>26,6; 51,58</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,47; 41,36</t>
+          <t>9,34; 42,64</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>35,58; 73,03</t>
+          <t>38,28; 75,97</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>33,88; 87,42</t>
+          <t>59,18; 97,66</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20,03; 38,89</t>
+          <t>19,96; 39,27</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>43,86; 66,39</t>
+          <t>43,92; 67,32</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>23,41; 55,2</t>
+          <t>42,71; 63,97</t>
         </is>
       </c>
     </row>
